--- a/data/trans_orig/P55S_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P55S_R-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>10508</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>14949</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>63,59%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9190</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17277</t>
+          <t>17526</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>74,55%</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,69%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9893</t>
+          <t>9890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14252</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>86,3%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9493</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11135</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17140</t>
+          <t>17145</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>13443</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22520</t>
+          <t>22591</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>8379</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15952</t>
+          <t>16164</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17014</t>
+          <t>18116</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50840</t>
+          <t>50812</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>63265</t>
+          <t>63310</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14741</t>
+          <t>15214</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22303</t>
+          <t>22499</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>69138</t>
+          <t>70297</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>83441</t>
+          <t>83397</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>836</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>945</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9091</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14813</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16110</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>10783</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10644</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>11550</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14505</t>
+          <t>14206</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26796</t>
+          <t>26505</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28430</t>
+          <t>28504</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42094</t>
+          <t>42282</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,55%</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>17451</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35114</t>
+          <t>36765</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17240</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>35720</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>10257</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>93836</t>
+          <t>92807</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>115385</t>
+          <t>114501</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>93878</t>
+          <t>92864</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>116127</t>
+          <t>115384</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,6%</t>
         </is>
       </c>
     </row>
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17665</t>
+          <t>16753</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17606</t>
+          <t>18267</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8978</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22788</t>
+          <t>22591</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>37231</t>
+          <t>36422</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>61369</t>
+          <t>61772</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>50361</t>
+          <t>50924</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>76993</t>
+          <t>78033</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>19388</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>93830</t>
+          <t>95517</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>111202</t>
+          <t>112116</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>142671</t>
+          <t>143405</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>170169</t>
+          <t>171563</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>242664</t>
+          <t>243818</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>276184</t>
+          <t>276047</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13387</t>
+          <t>14318</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>23850</t>
+          <t>23526</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>31810</t>
+          <t>32718</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6059</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,19%</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>58,94%</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8613</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>15263</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>9857</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>12429</t>
+          <t>12734</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10950</t>
+          <t>11198</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21241</t>
+          <t>21954</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15569</t>
+          <t>15611</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>20768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34890</t>
+          <t>34292</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>78,94%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10095</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11876</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18384</t>
+          <t>18699</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9164</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22944</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8781</t>
+          <t>8849</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>9947</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44332</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59065</t>
+          <t>59052</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19694</t>
+          <t>19709</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>57991</t>
+          <t>59095</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>75377</t>
+          <t>75607</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15187</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13047</t>
+          <t>12917</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28599</t>
+          <t>28073</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18651</t>
+          <t>17298</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36565</t>
+          <t>36401</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>20251</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30881</t>
+          <t>31762</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>46343</t>
+          <t>46220</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>63929</t>
+          <t>63801</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>71063</t>
+          <t>70883</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>90651</t>
+          <t>92327</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>77,2%</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>9663</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16655</t>
+          <t>16055</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36014</t>
+          <t>37256</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16655</t>
+          <t>16055</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>36014</t>
+          <t>37256</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17820</t>
+          <t>17030</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>36812</t>
+          <t>36476</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17820</t>
+          <t>17030</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>36812</t>
+          <t>36476</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>76315</t>
+          <t>75213</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>99301</t>
+          <t>99911</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>76315</t>
+          <t>75213</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>99301</t>
+          <t>99911</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,82%</t>
         </is>
       </c>
     </row>
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>934</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>29821</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>30638</t>
+          <t>29997</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>57237</t>
+          <t>56437</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>47225</t>
+          <t>47001</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>77013</t>
+          <t>78954</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21947</t>
+          <t>21118</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>40160</t>
+          <t>40012</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>66469</t>
+          <t>67917</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>51240</t>
+          <t>50345</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>80674</t>
+          <t>82067</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>95066</t>
+          <t>94950</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>118364</t>
+          <t>117915</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>161192</t>
+          <t>160368</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>194857</t>
+          <t>193991</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>264005</t>
+          <t>264337</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>303379</t>
+          <t>304213</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,63%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>15764</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>12705</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>23224</t>
+          <t>22767</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9217,12 +9217,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9252,12 +9252,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,46%</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>40,87%</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2545</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>11457</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>76,01%</t>
         </is>
       </c>
     </row>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9806,12 +9806,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>52,87%</t>
         </is>
       </c>
     </row>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5874</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14054</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,82%</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -10305,12 +10305,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>13139</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,08%</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14744</t>
+          <t>14728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13853</t>
+          <t>14082</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15065</t>
+          <t>15390</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26568</t>
+          <t>27148</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>82,81%</t>
         </is>
       </c>
     </row>
@@ -10679,12 +10679,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9032</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>972</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -10874,12 +10874,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2297</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12510</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18349</t>
+          <t>17373</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10959,12 +10959,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>13508</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11072,12 +11072,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -11100,12 +11100,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25662</t>
+          <t>26442</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35068</t>
+          <t>35735</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11135,12 +11135,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>15654</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27325</t>
+          <t>27351</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11150,12 +11150,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>44877</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>59922</t>
+          <t>60199</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,82%</t>
         </is>
       </c>
     </row>
@@ -11248,12 +11248,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>969</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7816</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11263,12 +11263,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>969</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -11443,12 +11443,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12923</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18096</t>
+          <t>18670</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11596,7 +11596,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -11669,12 +11669,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31718</t>
+          <t>31993</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42180</t>
+          <t>42208</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32182</t>
+          <t>32243</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45913</t>
+          <t>45724</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>68970</t>
+          <t>68738</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>85640</t>
+          <t>85079</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>84,78%</t>
         </is>
       </c>
     </row>
@@ -11787,7 +11787,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11817,12 +11817,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10644</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11832,12 +11832,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2362</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>13587</t>
+          <t>14027</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11867,12 +11867,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11403</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30104</t>
+          <t>29414</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12082,12 +12082,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11403</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30104</t>
+          <t>29414</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -12160,12 +12160,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24876</t>
+          <t>23728</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12195,12 +12195,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24876</t>
+          <t>23728</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -12273,12 +12273,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>90813</t>
+          <t>91124</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>115894</t>
+          <t>115539</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12308,12 +12308,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>90813</t>
+          <t>91124</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>115894</t>
+          <t>115539</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17415</t>
+          <t>17818</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17415</t>
+          <t>17818</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -12581,12 +12581,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26023</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12616,12 +12616,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>29514</t>
+          <t>29966</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>57463</t>
+          <t>56150</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>45109</t>
+          <t>44829</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>74663</t>
+          <t>76956</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12666,12 +12666,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -12694,12 +12694,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12475</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12729,12 +12729,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12849</t>
+          <t>13263</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>34333</t>
+          <t>32716</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12764,12 +12764,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>19309</t>
+          <t>18673</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>40778</t>
+          <t>40440</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12807,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>85574</t>
+          <t>86182</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>102806</t>
+          <t>102965</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>159259</t>
+          <t>161657</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>193879</t>
+          <t>195735</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>254982</t>
+          <t>254357</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>291707</t>
+          <t>291250</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,53%</t>
         </is>
       </c>
     </row>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12940,7 +12940,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>14166</t>
+          <t>14308</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>33609</t>
+          <t>33361</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>15320</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>38261</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -13379,32 +13379,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13414,32 +13414,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7856</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13449,17 +13449,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11502</t>
+          <t>13338</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13469,12 +13469,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -13492,7 +13492,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -13502,12 +13502,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>669</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -13537,12 +13537,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13562,32 +13562,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>509</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -13605,32 +13605,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13640,32 +13640,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10743</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13675,32 +13675,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>14288</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10281</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>19369</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>70,45%</t>
         </is>
       </c>
     </row>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -13728,12 +13728,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -13763,12 +13763,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -13778,7 +13778,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13788,32 +13788,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -13831,17 +13831,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>12501</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>12501</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>12501</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13866,17 +13866,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13858</t>
+          <t>14991</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13858</t>
+          <t>14991</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13858</t>
+          <t>14991</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13901,17 +13901,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>25853</t>
+          <t>27492</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25853</t>
+          <t>27492</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25853</t>
+          <t>27492</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -13948,32 +13948,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -13983,32 +13983,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>579</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14018,32 +14018,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -14061,7 +14061,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -14071,12 +14071,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3608</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14096,32 +14096,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14131,32 +14131,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -14174,32 +14174,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11585</t>
+          <t>12690</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7762</t>
+          <t>8657</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>15568</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14209,32 +14209,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>10541</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14244,32 +14244,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>18147</t>
+          <t>20264</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13914</t>
+          <t>15521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22312</t>
+          <t>24717</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>72,08%</t>
         </is>
       </c>
     </row>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -14297,12 +14297,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14322,32 +14322,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14357,32 +14357,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -14400,17 +14400,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17457</t>
+          <t>18759</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17457</t>
+          <t>18759</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17457</t>
+          <t>18759</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14435,17 +14435,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14470,17 +14470,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>31175</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31175</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31175</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14517,32 +14517,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14552,32 +14552,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14587,32 +14587,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -14630,32 +14630,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14665,32 +14665,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14700,32 +14700,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>12492</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15437</t>
+          <t>17767</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>38,07%</t>
         </is>
       </c>
     </row>
@@ -14743,32 +14743,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13888</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16307</t>
+          <t>17496</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14778,32 +14778,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11849</t>
+          <t>13207</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15259</t>
+          <t>17181</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14813,32 +14813,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>25051</t>
+          <t>27094</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19994</t>
+          <t>21833</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29544</t>
+          <t>32228</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,06%</t>
         </is>
       </c>
     </row>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>558</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -14866,12 +14866,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>558</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -14936,12 +14936,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -14969,17 +14969,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21187</t>
+          <t>22790</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21187</t>
+          <t>22790</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21187</t>
+          <t>22790</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15004,17 +15004,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21179</t>
+          <t>23874</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21179</t>
+          <t>23874</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21179</t>
+          <t>23874</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>42367</t>
+          <t>46664</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>42367</t>
+          <t>46664</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>42367</t>
+          <t>46664</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15086,32 +15086,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>13296</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15121,32 +15121,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15156,32 +15156,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11972</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17441</t>
+          <t>17950</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -15199,32 +15199,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>18993</t>
+          <t>20501</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>14725</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25705</t>
+          <t>27657</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15234,32 +15234,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8660</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15269,32 +15269,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>27653</t>
+          <t>30146</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21507</t>
+          <t>23165</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35599</t>
+          <t>37370</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -15312,32 +15312,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>43614</t>
+          <t>46370</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36721</t>
+          <t>38891</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50650</t>
+          <t>53443</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15347,32 +15347,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21063</t>
+          <t>22491</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28710</t>
+          <t>31223</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15382,32 +15382,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>68847</t>
+          <t>73423</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>60588</t>
+          <t>64836</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>76663</t>
+          <t>81634</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,61%</t>
         </is>
       </c>
     </row>
@@ -15425,32 +15425,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15460,7 +15460,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -15470,12 +15470,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15495,32 +15495,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>700</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -15538,17 +15538,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>72035</t>
+          <t>77139</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>72035</t>
+          <t>77139</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>72035</t>
+          <t>77139</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15573,17 +15573,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>41839</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>41839</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>41839</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15608,17 +15608,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>110819</t>
+          <t>118978</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>110819</t>
+          <t>118978</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>110819</t>
+          <t>118978</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15655,32 +15655,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>967</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15690,32 +15690,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8794</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>13408</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15725,32 +15725,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>11589</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>7887</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15275</t>
+          <t>17412</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -15768,32 +15768,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>9178</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15803,32 +15803,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>27395</t>
+          <t>28872</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21834</t>
+          <t>22861</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33363</t>
+          <t>36037</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15838,32 +15838,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>32724</t>
+          <t>34110</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25987</t>
+          <t>26955</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40098</t>
+          <t>41442</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -15881,32 +15881,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>19113</t>
+          <t>21532</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>16755</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>25458</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15916,32 +15916,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>52498</t>
+          <t>57277</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>46436</t>
+          <t>50727</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58944</t>
+          <t>64578</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15951,32 +15951,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>71611</t>
+          <t>78808</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>63633</t>
+          <t>70655</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>79086</t>
+          <t>87014</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>65,12%</t>
         </is>
       </c>
     </row>
@@ -15994,32 +15994,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16029,32 +16029,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9131</t>
+          <t>10405</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16064,17 +16064,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>8413</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>12881</t>
+          <t>14425</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16084,12 +16084,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -16107,17 +16107,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>30066</t>
+          <t>32881</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30066</t>
+          <t>32881</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30066</t>
+          <t>32881</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16142,17 +16142,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>93201</t>
+          <t>100738</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>93201</t>
+          <t>100738</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>93201</t>
+          <t>100738</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16177,17 +16177,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>123267</t>
+          <t>133619</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>123267</t>
+          <t>133619</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>123267</t>
+          <t>133619</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16209,7 +16209,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -16259,32 +16259,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>25430</t>
+          <t>28337</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>21503</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32535</t>
+          <t>36638</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16294,32 +16294,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>25430</t>
+          <t>28337</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19367</t>
+          <t>21031</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32457</t>
+          <t>37045</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -16372,32 +16372,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>33673</t>
+          <t>35474</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27411</t>
+          <t>28240</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>41633</t>
+          <t>42921</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16407,32 +16407,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>33673</t>
+          <t>35474</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>27019</t>
+          <t>28094</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>41439</t>
+          <t>44216</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -16485,32 +16485,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>77668</t>
+          <t>83356</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>69279</t>
+          <t>74747</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>85881</t>
+          <t>92457</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16520,32 +16520,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>79813</t>
+          <t>85560</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>71389</t>
+          <t>75534</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>88075</t>
+          <t>95129</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -16598,32 +16598,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>8821</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16633,32 +16633,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7889</t>
+          <t>8840</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -16676,17 +16676,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -16711,17 +16711,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>141000</t>
+          <t>152090</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>141000</t>
+          <t>152090</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>141000</t>
+          <t>152090</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -16746,17 +16746,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>143145</t>
+          <t>154294</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>143145</t>
+          <t>154294</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>143145</t>
+          <t>154294</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -16793,32 +16793,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>19724</t>
+          <t>20782</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>14388</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>27305</t>
+          <t>27749</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16828,32 +16828,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>45966</t>
+          <t>50758</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>37908</t>
+          <t>40728</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>56721</t>
+          <t>60474</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16863,32 +16863,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>65690</t>
+          <t>71540</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>54805</t>
+          <t>59663</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>76049</t>
+          <t>84056</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -16906,32 +16906,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>30906</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>23168</t>
+          <t>25811</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>38840</t>
+          <t>41783</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16941,32 +16941,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>79747</t>
+          <t>85543</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>68817</t>
+          <t>73703</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>90374</t>
+          <t>97448</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16976,32 +16976,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>110653</t>
+          <t>118625</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>96697</t>
+          <t>104977</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>123897</t>
+          <t>134918</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -17019,32 +17019,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>95856</t>
+          <t>103326</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>85974</t>
+          <t>93352</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>104837</t>
+          <t>113604</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17054,32 +17054,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>181901</t>
+          <t>197156</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>167571</t>
+          <t>183692</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>193909</t>
+          <t>209926</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17089,32 +17089,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>277757</t>
+          <t>300482</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>263702</t>
+          <t>281844</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>294117</t>
+          <t>316520</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,42%</t>
         </is>
       </c>
     </row>
@@ -17132,32 +17132,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13450</t>
+          <t>15083</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17167,32 +17167,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>14127</t>
+          <t>15606</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>10545</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>19771</t>
+          <t>22099</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17202,22 +17202,22 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>22526</t>
+          <t>24691</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>16765</t>
+          <t>18148</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>30154</t>
+          <t>33629</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -17227,7 +17227,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -17245,17 +17245,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>154885</t>
+          <t>166274</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>154885</t>
+          <t>166274</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>154885</t>
+          <t>166274</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17280,17 +17280,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>321741</t>
+          <t>349063</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>321741</t>
+          <t>349063</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>321741</t>
+          <t>349063</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17315,17 +17315,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>476626</t>
+          <t>515337</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>476626</t>
+          <t>515337</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>476626</t>
+          <t>515337</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
